--- a/nr-prepare-release-1.1.0-final/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/nr-prepare-release-1.1.0-final/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T16:54:59+00:00</t>
+    <t>2025-02-11T12:39:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -473,10 +473,7 @@
   </si>
   <si>
     <t>typeBAL : Type de boîte aux lettres.
-Valeurs possibles :
-ORG pour une BAL organisationnelle;
-APP pour une BAL applicative;
-PER pour une BAL personnelle, rattachée à une personne physique</t>
+Valeurs possibles : ORG | APP | PER | CAB</t>
   </si>
   <si>
     <t>ContactPoint.extension:as-mailbox-mss-metadata.extension:type.id</t>
